--- a/output/pdf_financials_xlsx/AWR.xlsx
+++ b/output/pdf_financials_xlsx/AWR.xlsx
@@ -1932,13 +1932,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.35296</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.35296</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.35296</v>
       </c>
     </row>
     <row r="93">
@@ -2339,10 +2339,10 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0.04545</v>
+        <v>-0.042593</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-0.000803</v>
       </c>
       <c r="D118" s="3" t="n">
         <v>0</v>
@@ -3207,7 +3207,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -3587,7 +3591,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="n">
         <v>1.35296</v>
       </c>
@@ -3990,7 +3998,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E43" s="5" t="n">
         <v>-0.088043</v>
       </c>

--- a/output/pdf_financials_xlsx/AWR.xlsx
+++ b/output/pdf_financials_xlsx/AWR.xlsx
@@ -980,13 +980,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.069997</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.00496</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.02914</v>
       </c>
     </row>
     <row r="35">
@@ -1012,13 +1012,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.069997</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.00496</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.02914</v>
       </c>
     </row>
     <row r="37">
@@ -1204,13 +1204,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.097376</v>
+        <v>0.027379</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.840155</v>
+        <v>0.835195</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.06616900000000001</v>
+        <v>0.037029</v>
       </c>
     </row>
     <row r="49">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/AWR.xlsx
+++ b/output/pdf_financials_xlsx/AWR.xlsx
@@ -676,7 +676,7 @@
         <v>-4.061348</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-0.357412</v>
+        <v>-0.347578</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-0.357412</v>
@@ -692,7 +692,7 @@
         <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.009834000000000001</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
@@ -868,7 +868,7 @@
         <v>-4.061348</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.357412</v>
+        <v>-0.347578</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.357412</v>
@@ -900,7 +900,7 @@
         <v>-4.061348</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.357412</v>
+        <v>-0.347578</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.357412</v>
@@ -938,7 +938,7 @@
         <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0</v>
+        <v>-2.829292993227419</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -2297,7 +2297,7 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0.0575</v>
+        <v>0.1465</v>
       </c>
     </row>
     <row r="116">
@@ -4031,7 +4031,11 @@
           <t>Proceeds from sale of investments 6</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -5066,7 +5070,11 @@
           <t>Income tax recovery</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
